--- a/rag/eval/results_new30/SuppFile2_Stats_generated.xlsx
+++ b/rag/eval/results_new30/SuppFile2_Stats_generated.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IndividQuest_FisherExact(Tab3)" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ModelComp_SignedRankFig4" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ModelComp_BH_AdjustFig4" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="IndividQuest_FisherExact(Tab3)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ModelComp_SignedRankFig4" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ModelComp_BH_AdjustFig4" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -818,7 +818,7 @@
         <v>1</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.127</v>
+        <v>0.0958</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>1</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.724</v>
+        <v>0.548</v>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>1</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.712</v>
+        <v>0.555</v>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         <v>4</v>
       </c>
       <c r="Z30" t="n">
-        <v>1</v>
+        <v>0.981</v>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
@@ -4051,7 +4051,7 @@
         <v>2</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1</v>
+        <v>0.992</v>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
@@ -4164,7 +4164,7 @@
         <v>1</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0.916</v>
+        <v>0.624</v>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
         <v>3</v>
       </c>
       <c r="Z38" t="n">
-        <v>0.485</v>
+        <v>0.441</v>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>2</v>
       </c>
       <c r="AE38" t="n">
-        <v>0.752</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="AF38" t="inlineStr">
         <is>
@@ -4590,7 +4590,7 @@
         <v>2</v>
       </c>
       <c r="Z39" t="n">
-        <v>0.429</v>
+        <v>0.418</v>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
@@ -4618,7 +4618,7 @@
         <v>1</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0.231</v>
+        <v>0.315</v>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         <v>3</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0.843</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
@@ -5268,7 +5268,7 @@
         <v>1</v>
       </c>
       <c r="Z45" t="n">
-        <v>0.378</v>
+        <v>0.515</v>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
@@ -5296,7 +5296,7 @@
         <v>2</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0.378</v>
+        <v>0.515</v>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
         <v>8</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0.899</v>
+        <v>0.953</v>
       </c>
       <c r="AK47" t="inlineStr">
         <is>
@@ -5607,7 +5607,7 @@
         <v>7</v>
       </c>
       <c r="Z48" t="n">
-        <v>1</v>
+        <v>0.981</v>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
@@ -5861,7 +5861,7 @@
         <v>6</v>
       </c>
       <c r="AJ50" t="n">
-        <v>1</v>
+        <v>0.992</v>
       </c>
       <c r="AK50" t="inlineStr">
         <is>
@@ -6286,7 +6286,7 @@
         <v>1</v>
       </c>
       <c r="Z55" t="n">
-        <v>0.127</v>
+        <v>0.0958</v>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
         <v>3</v>
       </c>
       <c r="AE55" t="n">
-        <v>0.724</v>
+        <v>0.548</v>
       </c>
       <c r="AF55" t="inlineStr">
         <is>
@@ -7331,7 +7331,7 @@
         <v>3</v>
       </c>
       <c r="AJ64" t="n">
-        <v>0.899</v>
+        <v>0.953</v>
       </c>
       <c r="AK64" t="inlineStr">
         <is>
@@ -7416,7 +7416,7 @@
         <v>4</v>
       </c>
       <c r="Z65" t="n">
-        <v>1</v>
+        <v>0.981</v>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
@@ -7670,7 +7670,7 @@
         <v>4</v>
       </c>
       <c r="AJ67" t="n">
-        <v>1</v>
+        <v>0.992</v>
       </c>
       <c r="AK67" t="inlineStr">
         <is>
@@ -7769,7 +7769,7 @@
         <v>1</v>
       </c>
       <c r="AE68" t="n">
-        <v>0.393</v>
+        <v>0.536</v>
       </c>
       <c r="AF68" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         <v>1</v>
       </c>
       <c r="AJ68" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.332</v>
       </c>
       <c r="AK68" t="inlineStr">
         <is>
@@ -7896,7 +7896,7 @@
         <v>2</v>
       </c>
       <c r="AJ69" t="n">
-        <v>0.712</v>
+        <v>0.498</v>
       </c>
       <c r="AK69" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
         <v>1</v>
       </c>
       <c r="AJ72" t="n">
-        <v>0.378</v>
+        <v>0.343</v>
       </c>
       <c r="AK72" t="inlineStr">
         <is>
@@ -8209,7 +8209,7 @@
         <v>1</v>
       </c>
       <c r="Z74" t="n">
-        <v>0.158</v>
+        <v>0.216</v>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
@@ -8223,7 +8223,7 @@
         <v>1</v>
       </c>
       <c r="AE74" t="n">
-        <v>0.622</v>
+        <v>0.848</v>
       </c>
       <c r="AF74" t="inlineStr">
         <is>
@@ -8322,7 +8322,7 @@
         <v>3</v>
       </c>
       <c r="Z75" t="n">
-        <v>0.869</v>
+        <v>1</v>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
@@ -8576,7 +8576,7 @@
         <v>5</v>
       </c>
       <c r="AJ77" t="n">
-        <v>1</v>
+        <v>0.806</v>
       </c>
       <c r="AK77" t="inlineStr">
         <is>
@@ -8887,7 +8887,7 @@
         <v>2</v>
       </c>
       <c r="Z80" t="n">
-        <v>0.378</v>
+        <v>0.515</v>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
@@ -8915,7 +8915,7 @@
         <v>2</v>
       </c>
       <c r="AJ80" t="n">
-        <v>0.378</v>
+        <v>0.515</v>
       </c>
       <c r="AK80" t="inlineStr">
         <is>
@@ -9141,7 +9141,7 @@
         <v>6</v>
       </c>
       <c r="AJ82" t="n">
-        <v>0.899</v>
+        <v>0.953</v>
       </c>
       <c r="AK82" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
         <v>8</v>
       </c>
       <c r="Z83" t="n">
-        <v>1</v>
+        <v>0.981</v>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
@@ -9480,7 +9480,7 @@
         <v>8</v>
       </c>
       <c r="AJ85" t="n">
-        <v>1</v>
+        <v>0.992</v>
       </c>
       <c r="AK85" t="inlineStr">
         <is>
@@ -9820,7 +9820,7 @@
         <v>5</v>
       </c>
       <c r="AJ89" t="n">
-        <v>0.378</v>
+        <v>0.343</v>
       </c>
       <c r="AK89" t="inlineStr">
         <is>
@@ -9905,7 +9905,7 @@
         <v>3</v>
       </c>
       <c r="Z90" t="n">
-        <v>0.191</v>
+        <v>0.156</v>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
@@ -9919,7 +9919,7 @@
         <v>2</v>
       </c>
       <c r="AE90" t="n">
-        <v>0.752</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="AF90" t="inlineStr">
         <is>
@@ -10357,7 +10357,7 @@
         <v>2</v>
       </c>
       <c r="Z94" t="n">
-        <v>0.924</v>
+        <v>0.42</v>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
@@ -10381,15 +10381,15 @@
       <c r="AH94" t="n">
         <v>0.008840000000000001</v>
       </c>
-      <c r="AI94" t="n">
+      <c r="AI94" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="AJ94" t="n">
-        <v>0.09719999999999999</v>
-      </c>
-      <c r="AK94" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="AJ94" s="3" t="n">
+        <v>0.0442</v>
+      </c>
+      <c r="AK94" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -10470,7 +10470,7 @@
         <v>5</v>
       </c>
       <c r="Z95" t="n">
-        <v>1</v>
+        <v>0.79</v>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
@@ -10498,7 +10498,7 @@
         <v>1</v>
       </c>
       <c r="AJ95" s="3" t="n">
-        <v>0.0334</v>
+        <v>0.0152</v>
       </c>
       <c r="AK95" s="3" t="inlineStr">
         <is>
@@ -10950,7 +10950,7 @@
         <v>10</v>
       </c>
       <c r="AJ99" t="n">
-        <v>0.899</v>
+        <v>0.953</v>
       </c>
       <c r="AK99" t="inlineStr">
         <is>
@@ -11035,7 +11035,7 @@
         <v>1</v>
       </c>
       <c r="Z100" t="n">
-        <v>0.788</v>
+        <v>0.537</v>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
@@ -11063,7 +11063,7 @@
         <v>2</v>
       </c>
       <c r="AJ100" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.0587</v>
       </c>
       <c r="AK100" t="inlineStr">
         <is>
@@ -11261,7 +11261,7 @@
         <v>4</v>
       </c>
       <c r="Z102" t="n">
-        <v>1</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
@@ -11289,7 +11289,7 @@
         <v>4</v>
       </c>
       <c r="AJ102" t="n">
-        <v>0.48</v>
+        <v>0.327</v>
       </c>
       <c r="AK102" t="inlineStr">
         <is>
@@ -11402,7 +11402,7 @@
         <v>8</v>
       </c>
       <c r="AJ103" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.752</v>
       </c>
       <c r="AK103" t="inlineStr">
         <is>
@@ -11515,7 +11515,7 @@
         <v>9</v>
       </c>
       <c r="AJ104" t="n">
-        <v>0.9</v>
+        <v>0.737</v>
       </c>
       <c r="AK104" t="inlineStr">
         <is>
@@ -15627,7 +15627,7 @@
         <v>3</v>
       </c>
       <c r="I2" t="n">
-        <v>0.132</v>
+        <v>0.163</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -15641,7 +15641,7 @@
         <v>9</v>
       </c>
       <c r="N2" t="n">
-        <v>0.67</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0311</v>
+        <v>0.0424</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -15669,7 +15669,7 @@
         <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0614</v>
+        <v>0.0772</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -15706,7 +15706,7 @@
         <v>4</v>
       </c>
       <c r="I3" t="n">
-        <v>0.21</v>
+        <v>0.242</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -15720,7 +15720,7 @@
         <v>8</v>
       </c>
       <c r="N3" t="n">
-        <v>0.635</v>
+        <v>0.645</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -15734,7 +15734,7 @@
         <v>2</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0851</v>
+        <v>0.0929</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -15748,7 +15748,7 @@
         <v>3</v>
       </c>
       <c r="X3" t="n">
-        <v>0.132</v>
+        <v>0.162</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -15785,7 +15785,7 @@
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>0.126</v>
+        <v>0.143</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -15799,7 +15799,7 @@
         <v>5</v>
       </c>
       <c r="N4" t="n">
-        <v>0.471</v>
+        <v>0.493</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -15813,7 +15813,7 @@
         <v>3</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0851</v>
+        <v>0.0929</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -15827,7 +15827,7 @@
         <v>2</v>
       </c>
       <c r="X4" t="n">
-        <v>0.132</v>
+        <v>0.162</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -15864,7 +15864,7 @@
         <v>2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.132</v>
+        <v>0.162</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -15878,7 +15878,7 @@
         <v>1</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0931</v>
+        <v>0.109</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -15906,7 +15906,7 @@
         <v>6</v>
       </c>
       <c r="X5" t="n">
-        <v>0.392</v>
+        <v>0.415</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -15943,7 +15943,7 @@
         <v>8</v>
       </c>
       <c r="I6" t="n">
-        <v>0.489</v>
+        <v>0.497</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -15957,7 +15957,7 @@
         <v>4</v>
       </c>
       <c r="N6" t="n">
-        <v>0.347</v>
+        <v>0.358</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -15971,7 +15971,7 @@
         <v>4</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0931</v>
+        <v>0.109</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -15985,7 +15985,7 @@
         <v>4</v>
       </c>
       <c r="X6" t="n">
-        <v>0.132</v>
+        <v>0.162</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -16022,7 +16022,7 @@
         <v>9</v>
       </c>
       <c r="I7" t="n">
-        <v>0.732</v>
+        <v>0.749</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -16036,7 +16036,7 @@
         <v>2</v>
       </c>
       <c r="N7" t="n">
-        <v>0.126</v>
+        <v>0.143</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -16050,7 +16050,7 @@
         <v>5</v>
       </c>
       <c r="S7" t="n">
-        <v>0.229</v>
+        <v>0.268</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -16064,7 +16064,7 @@
         <v>8</v>
       </c>
       <c r="X7" t="n">
-        <v>0.392</v>
+        <v>0.417</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -16101,7 +16101,7 @@
         <v>5</v>
       </c>
       <c r="I8" t="n">
-        <v>0.229</v>
+        <v>0.268</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -16115,7 +16115,7 @@
         <v>3</v>
       </c>
       <c r="N8" t="n">
-        <v>0.132</v>
+        <v>0.163</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -16129,7 +16129,7 @@
         <v>8</v>
       </c>
       <c r="S8" t="n">
-        <v>0.705</v>
+        <v>0.717</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -16143,7 +16143,7 @@
         <v>7</v>
       </c>
       <c r="X8" t="n">
-        <v>0.392</v>
+        <v>0.417</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -16180,7 +16180,7 @@
         <v>7</v>
       </c>
       <c r="I9" t="n">
-        <v>0.321</v>
+        <v>0.328</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -16194,7 +16194,7 @@
         <v>6</v>
       </c>
       <c r="N9" t="n">
-        <v>0.489</v>
+        <v>0.497</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -16208,7 +16208,7 @@
         <v>6</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.583</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -16222,7 +16222,7 @@
         <v>5</v>
       </c>
       <c r="X9" t="n">
-        <v>0.15</v>
+        <v>0.178</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -16259,7 +16259,7 @@
         <v>6</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3</v>
+        <v>0.303</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -16273,7 +16273,7 @@
         <v>7</v>
       </c>
       <c r="N10" t="n">
-        <v>0.494</v>
+        <v>0.505</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -16287,7 +16287,7 @@
         <v>7</v>
       </c>
       <c r="S10" t="n">
-        <v>0.699</v>
+        <v>0.706</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -16339,7 +16339,7 @@
         <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>0.142</v>
+        <v>0.171</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -16353,7 +16353,7 @@
         <v>5</v>
       </c>
       <c r="N12" t="n">
-        <v>0.0958</v>
+        <v>0.118</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -16367,7 +16367,7 @@
         <v>1</v>
       </c>
       <c r="S12" t="n">
-        <v>0.00673</v>
+        <v>0.009180000000000001</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -16381,7 +16381,7 @@
         <v>1</v>
       </c>
       <c r="X12" t="n">
-        <v>0.0288</v>
+        <v>0.0333</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -16418,7 +16418,7 @@
         <v>4</v>
       </c>
       <c r="I13" t="n">
-        <v>0.152</v>
+        <v>0.183</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -16432,7 +16432,7 @@
         <v>6</v>
       </c>
       <c r="N13" t="n">
-        <v>0.142</v>
+        <v>0.171</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -16446,7 +16446,7 @@
         <v>2</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0326</v>
+        <v>0.0333</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -16460,7 +16460,7 @@
         <v>2</v>
       </c>
       <c r="X13" t="n">
-        <v>0.0927</v>
+        <v>0.112</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -16497,7 +16497,7 @@
         <v>2</v>
       </c>
       <c r="I14" t="n">
-        <v>0.142</v>
+        <v>0.171</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -16511,7 +16511,7 @@
         <v>1</v>
       </c>
       <c r="N14" t="n">
-        <v>0.0644</v>
+        <v>0.0702</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -16539,7 +16539,7 @@
         <v>6</v>
       </c>
       <c r="X14" t="n">
-        <v>0.251</v>
+        <v>0.287</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -16576,7 +16576,7 @@
         <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0927</v>
+        <v>0.112</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -16590,7 +16590,7 @@
         <v>9</v>
       </c>
       <c r="N15" t="n">
-        <v>0.438</v>
+        <v>0.459</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -16604,7 +16604,7 @@
         <v>3</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0825</v>
+        <v>0.1</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -16618,7 +16618,7 @@
         <v>3</v>
       </c>
       <c r="X15" t="n">
-        <v>0.0958</v>
+        <v>0.118</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -16655,7 +16655,7 @@
         <v>9</v>
       </c>
       <c r="I16" t="n">
-        <v>0.575</v>
+        <v>0.599</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -16669,7 +16669,7 @@
         <v>2</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0927</v>
+        <v>0.112</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -16683,7 +16683,7 @@
         <v>4</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0927</v>
+        <v>0.112</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -16697,7 +16697,7 @@
         <v>4</v>
       </c>
       <c r="X16" t="n">
-        <v>0.142</v>
+        <v>0.171</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -16734,7 +16734,7 @@
         <v>6</v>
       </c>
       <c r="I17" t="n">
-        <v>0.205</v>
+        <v>0.231</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -16748,7 +16748,7 @@
         <v>3</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0927</v>
+        <v>0.112</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -16762,7 +16762,7 @@
         <v>7</v>
       </c>
       <c r="S17" t="n">
-        <v>0.438</v>
+        <v>0.459</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -16776,7 +16776,7 @@
         <v>9</v>
       </c>
       <c r="X17" t="n">
-        <v>0.478</v>
+        <v>0.504</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -16813,7 +16813,7 @@
         <v>8</v>
       </c>
       <c r="I18" t="n">
-        <v>0.438</v>
+        <v>0.459</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -16827,7 +16827,7 @@
         <v>4</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0927</v>
+        <v>0.112</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -16841,7 +16841,7 @@
         <v>5</v>
       </c>
       <c r="S18" t="n">
-        <v>0.184</v>
+        <v>0.206</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -16855,7 +16855,7 @@
         <v>7</v>
       </c>
       <c r="X18" t="n">
-        <v>0.438</v>
+        <v>0.459</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -16892,7 +16892,7 @@
         <v>7</v>
       </c>
       <c r="I19" t="n">
-        <v>0.377</v>
+        <v>0.395</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -16906,7 +16906,7 @@
         <v>8</v>
       </c>
       <c r="N19" t="n">
-        <v>0.428</v>
+        <v>0.451</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -16920,7 +16920,7 @@
         <v>6</v>
       </c>
       <c r="S19" t="n">
-        <v>0.438</v>
+        <v>0.459</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -16934,7 +16934,7 @@
         <v>5</v>
       </c>
       <c r="X19" t="n">
-        <v>0.162</v>
+        <v>0.183</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -16971,7 +16971,7 @@
         <v>5</v>
       </c>
       <c r="I20" t="n">
-        <v>0.178</v>
+        <v>0.197</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -16985,7 +16985,7 @@
         <v>7</v>
       </c>
       <c r="N20" t="n">
-        <v>0.179</v>
+        <v>0.2</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -16999,7 +16999,7 @@
         <v>8</v>
       </c>
       <c r="S20" t="n">
-        <v>0.738</v>
+        <v>0.733</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -17013,7 +17013,7 @@
         <v>8</v>
       </c>
       <c r="X20" t="n">
-        <v>0.438</v>
+        <v>0.459</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>

--- a/rag/eval/results_new30/SuppFile2_Stats_generated.xlsx
+++ b/rag/eval/results_new30/SuppFile2_Stats_generated.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="IndividQuest_FisherExact(Tab3)" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="ModelComp_SignedRankFig4" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="ModelComp_BH_AdjustFig4" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IndividQuest_FisherExact(Tab3)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ModelComp_SignedRankFig4" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ModelComp_BH_AdjustFig4" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1688,10 +1688,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G11" t="n">
         <v>4</v>
@@ -1700,16 +1700,16 @@
         <v>3</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>0.5333</v>
+        <v>0.5667</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.7647</v>
+        <v>0.7778</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0.5652</v>
+        <v>0.6087</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>0.65</v>
+        <v>0.6829</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1717,10 +1717,10 @@
         </is>
       </c>
       <c r="O11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q11" t="n">
         <v>4</v>
@@ -1729,16 +1729,16 @@
         <v>3</v>
       </c>
       <c r="S11" s="2" t="n">
-        <v>0.5333</v>
+        <v>0.5667</v>
       </c>
       <c r="T11" s="2" t="n">
-        <v>0.7647</v>
+        <v>0.7778</v>
       </c>
       <c r="U11" s="2" t="n">
-        <v>0.5652</v>
+        <v>0.6087</v>
       </c>
       <c r="V11" s="2" t="n">
-        <v>0.65</v>
+        <v>0.6829</v>
       </c>
       <c r="X11" t="n">
         <v>1</v>
@@ -3370,7 +3370,7 @@
         <v>0.5669999999999999</v>
       </c>
       <c r="AI26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AJ26" t="n">
         <v>1</v>
@@ -3512,10 +3512,10 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G28" t="n">
         <v>4</v>
@@ -3524,16 +3524,16 @@
         <v>3</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>0.5333</v>
+        <v>0.5667</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.7647</v>
+        <v>0.7778</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0.5652</v>
+        <v>0.6087</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>0.65</v>
+        <v>0.6829</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
         <v>0.7805</v>
       </c>
       <c r="X28" t="n">
-        <v>0.288</v>
+        <v>0.422</v>
       </c>
       <c r="Y28" t="n">
         <v>1</v>
@@ -3579,7 +3579,7 @@
         </is>
       </c>
       <c r="AC28" t="n">
-        <v>0.402</v>
+        <v>0.658</v>
       </c>
       <c r="AD28" t="n">
         <v>1</v>
@@ -3593,10 +3593,10 @@
         </is>
       </c>
       <c r="AH28" t="n">
-        <v>0.542</v>
+        <v>0.758</v>
       </c>
       <c r="AI28" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AJ28" t="n">
         <v>1</v>
@@ -3822,7 +3822,7 @@
         <v>0.66</v>
       </c>
       <c r="AI30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AJ30" t="n">
         <v>1</v>
@@ -10241,7 +10241,7 @@
         <v>0.438</v>
       </c>
       <c r="Y93" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z93" t="n">
         <v>1</v>
@@ -10779,10 +10779,10 @@
         </is>
       </c>
       <c r="O98" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P98" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q98" t="n">
         <v>2</v>
@@ -10791,22 +10791,22 @@
         <v>5</v>
       </c>
       <c r="S98" s="2" t="n">
-        <v>0.7</v>
+        <v>0.7333</v>
       </c>
       <c r="T98" s="2" t="n">
-        <v>0.8889</v>
+        <v>0.8947000000000001</v>
       </c>
       <c r="U98" s="2" t="n">
-        <v>0.6957</v>
+        <v>0.7391</v>
       </c>
       <c r="V98" s="2" t="n">
-        <v>0.7805</v>
+        <v>0.8095</v>
       </c>
       <c r="X98" t="n">
-        <v>0.589</v>
+        <v>0.412</v>
       </c>
       <c r="Y98" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Z98" t="n">
         <v>1</v>
@@ -10831,7 +10831,7 @@
         </is>
       </c>
       <c r="AH98" t="n">
-        <v>0.365</v>
+        <v>0.221</v>
       </c>
       <c r="AI98" t="n">
         <v>6</v>
@@ -11371,7 +11371,7 @@
         <v>0.58</v>
       </c>
       <c r="Y103" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z103" t="n">
         <v>1</v>
@@ -12103,7 +12103,7 @@
         <v>10</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>0.5333</v>
+        <v>0.5667</v>
       </c>
       <c r="D12" s="5" t="n">
         <v>0.7667</v>
@@ -12115,7 +12115,7 @@
         <v>10</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>0.7647</v>
+        <v>0.7778</v>
       </c>
       <c r="I12" s="5" t="n">
         <v>1</v>
@@ -12127,7 +12127,7 @@
         <v>10</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>0.5652</v>
+        <v>0.6087</v>
       </c>
       <c r="N12" s="5" t="n">
         <v>0.6957</v>
@@ -12139,7 +12139,7 @@
         <v>10</v>
       </c>
       <c r="R12" s="5" t="n">
-        <v>0.65</v>
+        <v>0.6829</v>
       </c>
       <c r="S12" s="5" t="n">
         <v>0.8205</v>
@@ -12994,7 +12994,7 @@
         <v>10</v>
       </c>
       <c r="C32" s="5" t="n">
-        <v>0.5333</v>
+        <v>0.5667</v>
       </c>
       <c r="D32" s="5" t="n">
         <v>0.7</v>
@@ -13006,7 +13006,7 @@
         <v>10</v>
       </c>
       <c r="H32" s="5" t="n">
-        <v>0.7647</v>
+        <v>0.7778</v>
       </c>
       <c r="I32" s="5" t="n">
         <v>1</v>
@@ -13018,7 +13018,7 @@
         <v>10</v>
       </c>
       <c r="M32" s="5" t="n">
-        <v>0.5652</v>
+        <v>0.6087</v>
       </c>
       <c r="N32" s="5" t="n">
         <v>0.6087</v>
@@ -13030,7 +13030,7 @@
         <v>10</v>
       </c>
       <c r="R32" s="5" t="n">
-        <v>0.65</v>
+        <v>0.6829</v>
       </c>
       <c r="S32" s="5" t="n">
         <v>0.7568</v>
@@ -14007,7 +14007,7 @@
         <v>0.8</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>0.7</v>
+        <v>0.7333</v>
       </c>
       <c r="G54" t="n">
         <v>10</v>
@@ -14019,7 +14019,7 @@
         <v>1</v>
       </c>
       <c r="J54" s="5" t="n">
-        <v>0.8889</v>
+        <v>0.8947000000000001</v>
       </c>
       <c r="L54" t="n">
         <v>10</v>
@@ -14031,7 +14031,7 @@
         <v>0.7391</v>
       </c>
       <c r="O54" s="5" t="n">
-        <v>0.6957</v>
+        <v>0.7391</v>
       </c>
       <c r="Q54" t="n">
         <v>10</v>
@@ -14043,7 +14043,7 @@
         <v>0.85</v>
       </c>
       <c r="T54" s="5" t="n">
-        <v>0.7805</v>
+        <v>0.8095</v>
       </c>
     </row>
     <row r="55">
@@ -14353,13 +14353,13 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>0.699</v>
+        <v>0.572</v>
       </c>
       <c r="D61" t="n">
         <v>0.177</v>
       </c>
       <c r="E61" t="n">
-        <v>0.0281</v>
+        <v>0.0253</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -14367,13 +14367,13 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>0.0274</v>
+        <v>0.0256</v>
       </c>
       <c r="I61" t="n">
         <v>0.404</v>
       </c>
       <c r="J61" t="n">
-        <v>0.353</v>
+        <v>0.359</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
@@ -14381,13 +14381,13 @@
         </is>
       </c>
       <c r="M61" t="n">
-        <v>0.123</v>
+        <v>0.09379999999999999</v>
       </c>
       <c r="N61" t="n">
         <v>0.635</v>
       </c>
       <c r="O61" t="n">
-        <v>0.00774</v>
+        <v>0.00705</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -14395,13 +14395,13 @@
         </is>
       </c>
       <c r="R61" t="n">
-        <v>0.285</v>
+        <v>0.235</v>
       </c>
       <c r="S61" t="n">
         <v>0.927</v>
       </c>
       <c r="T61" t="n">
-        <v>0.0388</v>
+        <v>0.0358</v>
       </c>
     </row>
     <row r="62">
@@ -14431,7 +14431,7 @@
         <v>0.11</v>
       </c>
       <c r="J62" t="n">
-        <v>0.382</v>
+        <v>0.421</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
@@ -14439,13 +14439,13 @@
         </is>
       </c>
       <c r="M62" t="n">
-        <v>0.117</v>
+        <v>0.09950000000000001</v>
       </c>
       <c r="N62" t="n">
         <v>0.721</v>
       </c>
       <c r="O62" t="n">
-        <v>0.015</v>
+        <v>0.012</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -15360,7 +15360,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>0.0487</v>
+        <v>0.0508</v>
       </c>
       <c r="D83" t="n">
         <v>0.0571</v>
@@ -15374,7 +15374,7 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>0.0122</v>
+        <v>0.0127</v>
       </c>
       <c r="I83" t="n">
         <v>0.594</v>
@@ -15388,7 +15388,7 @@
         </is>
       </c>
       <c r="M83" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.877</v>
       </c>
       <c r="N83" t="n">
         <v>0.000706</v>
@@ -15402,7 +15402,7 @@
         </is>
       </c>
       <c r="R83" t="n">
-        <v>0.27</v>
+        <v>0.289</v>
       </c>
       <c r="S83" t="n">
         <v>0.00279</v>
@@ -15418,7 +15418,7 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>0.06279999999999999</v>
+        <v>0.06270000000000001</v>
       </c>
       <c r="D84" t="n">
         <v>0.0712</v>
@@ -15446,7 +15446,7 @@
         </is>
       </c>
       <c r="M84" t="n">
-        <v>0.9370000000000001</v>
+        <v>1</v>
       </c>
       <c r="N84" t="n">
         <v>0.000153</v>
@@ -15627,7 +15627,7 @@
         <v>3</v>
       </c>
       <c r="I2" t="n">
-        <v>0.163</v>
+        <v>0.156</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -15641,7 +15641,7 @@
         <v>9</v>
       </c>
       <c r="N2" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.672</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -15669,7 +15669,7 @@
         <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0772</v>
+        <v>0.0806</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -15706,7 +15706,7 @@
         <v>4</v>
       </c>
       <c r="I3" t="n">
-        <v>0.242</v>
+        <v>0.233</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -15734,7 +15734,7 @@
         <v>2</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0929</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -15748,7 +15748,7 @@
         <v>3</v>
       </c>
       <c r="X3" t="n">
-        <v>0.162</v>
+        <v>0.156</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -15779,7 +15779,7 @@
         <v>0.05</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0281</v>
+        <v>0.0253</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
@@ -15793,13 +15793,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.353</v>
+        <v>0.359</v>
       </c>
       <c r="M4" t="n">
         <v>5</v>
       </c>
       <c r="N4" t="n">
-        <v>0.493</v>
+        <v>0.49</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -15807,13 +15807,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>0.00774</v>
+        <v>0.00705</v>
       </c>
       <c r="R4" t="n">
         <v>3</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0929</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -15821,13 +15821,13 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>0.0388</v>
+        <v>0.0358</v>
       </c>
       <c r="W4" t="n">
         <v>2</v>
       </c>
       <c r="X4" t="n">
-        <v>0.162</v>
+        <v>0.156</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -15858,13 +15858,13 @@
         <v>0.05</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0487</v>
+        <v>0.0508</v>
       </c>
       <c r="H5" t="n">
         <v>2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.162</v>
+        <v>0.156</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -15872,7 +15872,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.0122</v>
+        <v>0.0127</v>
       </c>
       <c r="M5" t="n">
         <v>1</v>
@@ -15886,13 +15886,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.877</v>
       </c>
       <c r="R5" t="n">
         <v>9</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -15900,13 +15900,13 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>0.27</v>
+        <v>0.289</v>
       </c>
       <c r="W5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X5" t="n">
-        <v>0.415</v>
+        <v>0.423</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -15985,7 +15985,7 @@
         <v>4</v>
       </c>
       <c r="X6" t="n">
-        <v>0.162</v>
+        <v>0.156</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -16016,13 +16016,13 @@
         <v>0.05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.699</v>
+        <v>0.572</v>
       </c>
       <c r="H7" t="n">
         <v>9</v>
       </c>
       <c r="I7" t="n">
-        <v>0.749</v>
+        <v>0.66</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -16030,7 +16030,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.0274</v>
+        <v>0.0256</v>
       </c>
       <c r="M7" t="n">
         <v>2</v>
@@ -16044,13 +16044,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>0.123</v>
+        <v>0.09379999999999999</v>
       </c>
       <c r="R7" t="n">
         <v>5</v>
       </c>
       <c r="S7" t="n">
-        <v>0.268</v>
+        <v>0.233</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -16058,13 +16058,13 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>0.285</v>
+        <v>0.235</v>
       </c>
       <c r="W7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="X7" t="n">
-        <v>0.417</v>
+        <v>0.371</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -16115,7 +16115,7 @@
         <v>3</v>
       </c>
       <c r="N8" t="n">
-        <v>0.163</v>
+        <v>0.156</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -16129,7 +16129,7 @@
         <v>8</v>
       </c>
       <c r="S8" t="n">
-        <v>0.717</v>
+        <v>0.704</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -16259,7 +16259,7 @@
         <v>6</v>
       </c>
       <c r="I10" t="n">
-        <v>0.303</v>
+        <v>0.319</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -16287,7 +16287,7 @@
         <v>7</v>
       </c>
       <c r="S10" t="n">
-        <v>0.706</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -16301,7 +16301,7 @@
         <v>9</v>
       </c>
       <c r="X10" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.927</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -16339,7 +16339,7 @@
         <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>0.171</v>
+        <v>0.17</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -16418,7 +16418,7 @@
         <v>4</v>
       </c>
       <c r="I13" t="n">
-        <v>0.183</v>
+        <v>0.177</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -16432,7 +16432,7 @@
         <v>6</v>
       </c>
       <c r="N13" t="n">
-        <v>0.171</v>
+        <v>0.17</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -16491,13 +16491,13 @@
         <v>0.05</v>
       </c>
       <c r="G14" t="n">
-        <v>0.06279999999999999</v>
+        <v>0.06270000000000001</v>
       </c>
       <c r="H14" t="n">
         <v>2</v>
       </c>
       <c r="I14" t="n">
-        <v>0.171</v>
+        <v>0.17</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -16519,13 +16519,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>0.9370000000000001</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>9</v>
       </c>
       <c r="S14" t="n">
-        <v>0.9370000000000001</v>
+        <v>1</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -16584,13 +16584,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0.382</v>
+        <v>0.421</v>
       </c>
       <c r="M15" t="n">
         <v>9</v>
       </c>
       <c r="N15" t="n">
-        <v>0.459</v>
+        <v>0.486</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -16598,13 +16598,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>0.015</v>
+        <v>0.012</v>
       </c>
       <c r="R15" t="n">
         <v>3</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -16697,7 +16697,7 @@
         <v>4</v>
       </c>
       <c r="X16" t="n">
-        <v>0.171</v>
+        <v>0.17</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -16762,7 +16762,7 @@
         <v>7</v>
       </c>
       <c r="S17" t="n">
-        <v>0.459</v>
+        <v>0.468</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -16813,7 +16813,7 @@
         <v>8</v>
       </c>
       <c r="I18" t="n">
-        <v>0.459</v>
+        <v>0.468</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -16835,13 +16835,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>0.117</v>
+        <v>0.09950000000000001</v>
       </c>
       <c r="R18" t="n">
         <v>5</v>
       </c>
       <c r="S18" t="n">
-        <v>0.206</v>
+        <v>0.193</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -16855,7 +16855,7 @@
         <v>7</v>
       </c>
       <c r="X18" t="n">
-        <v>0.459</v>
+        <v>0.468</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -16920,7 +16920,7 @@
         <v>6</v>
       </c>
       <c r="S19" t="n">
-        <v>0.459</v>
+        <v>0.468</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -17013,7 +17013,7 @@
         <v>8</v>
       </c>
       <c r="X20" t="n">
-        <v>0.459</v>
+        <v>0.468</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>

--- a/rag/eval/results_new30/SuppFile2_Stats_generated.xlsx
+++ b/rag/eval/results_new30/SuppFile2_Stats_generated.xlsx
@@ -818,7 +818,7 @@
         <v>1</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0958</v>
+        <v>0.115</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>1</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.548</v>
+        <v>0.658</v>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>1</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.555</v>
+        <v>0.592</v>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         <v>4</v>
       </c>
       <c r="Z30" t="n">
-        <v>0.981</v>
+        <v>1</v>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
@@ -3825,7 +3825,7 @@
         <v>4</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1</v>
+        <v>0.991</v>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
@@ -4051,7 +4051,7 @@
         <v>2</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0.992</v>
+        <v>0.881</v>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
@@ -4164,7 +4164,7 @@
         <v>1</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0.624</v>
+        <v>0.666</v>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
         <v>3</v>
       </c>
       <c r="Z38" t="n">
-        <v>0.441</v>
+        <v>0.471</v>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>2</v>
       </c>
       <c r="AE38" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.729</v>
       </c>
       <c r="AF38" t="inlineStr">
         <is>
@@ -4590,7 +4590,7 @@
         <v>2</v>
       </c>
       <c r="Z39" t="n">
-        <v>0.418</v>
+        <v>0.468</v>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
@@ -4618,7 +4618,7 @@
         <v>1</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0.315</v>
+        <v>0.252</v>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
@@ -5268,7 +5268,7 @@
         <v>1</v>
       </c>
       <c r="Z45" t="n">
-        <v>0.515</v>
+        <v>0.412</v>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
@@ -5296,7 +5296,7 @@
         <v>2</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0.515</v>
+        <v>0.412</v>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
         <v>8</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0.953</v>
+        <v>0.981</v>
       </c>
       <c r="AK47" t="inlineStr">
         <is>
@@ -5607,7 +5607,7 @@
         <v>7</v>
       </c>
       <c r="Z48" t="n">
-        <v>0.981</v>
+        <v>1</v>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
@@ -5635,7 +5635,7 @@
         <v>9</v>
       </c>
       <c r="AJ48" t="n">
-        <v>1</v>
+        <v>0.991</v>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
@@ -5861,7 +5861,7 @@
         <v>6</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0.992</v>
+        <v>0.881</v>
       </c>
       <c r="AK50" t="inlineStr">
         <is>
@@ -6286,7 +6286,7 @@
         <v>1</v>
       </c>
       <c r="Z55" t="n">
-        <v>0.0958</v>
+        <v>0.115</v>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
         <v>3</v>
       </c>
       <c r="AE55" t="n">
-        <v>0.548</v>
+        <v>0.658</v>
       </c>
       <c r="AF55" t="inlineStr">
         <is>
@@ -7331,7 +7331,7 @@
         <v>3</v>
       </c>
       <c r="AJ64" t="n">
-        <v>0.953</v>
+        <v>0.981</v>
       </c>
       <c r="AK64" t="inlineStr">
         <is>
@@ -7416,7 +7416,7 @@
         <v>4</v>
       </c>
       <c r="Z65" t="n">
-        <v>0.981</v>
+        <v>1</v>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         <v>5</v>
       </c>
       <c r="AJ65" t="n">
-        <v>1</v>
+        <v>0.991</v>
       </c>
       <c r="AK65" t="inlineStr">
         <is>
@@ -7670,7 +7670,7 @@
         <v>4</v>
       </c>
       <c r="AJ67" t="n">
-        <v>0.992</v>
+        <v>0.881</v>
       </c>
       <c r="AK67" t="inlineStr">
         <is>
@@ -7769,7 +7769,7 @@
         <v>1</v>
       </c>
       <c r="AE68" t="n">
-        <v>0.536</v>
+        <v>0.428</v>
       </c>
       <c r="AF68" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         <v>1</v>
       </c>
       <c r="AJ68" t="n">
-        <v>0.332</v>
+        <v>0.372</v>
       </c>
       <c r="AK68" t="inlineStr">
         <is>
@@ -7896,7 +7896,7 @@
         <v>2</v>
       </c>
       <c r="AJ69" t="n">
-        <v>0.498</v>
+        <v>0.592</v>
       </c>
       <c r="AK69" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
         <v>1</v>
       </c>
       <c r="AJ72" t="n">
-        <v>0.343</v>
+        <v>0.275</v>
       </c>
       <c r="AK72" t="inlineStr">
         <is>
@@ -8209,7 +8209,7 @@
         <v>1</v>
       </c>
       <c r="Z74" t="n">
-        <v>0.216</v>
+        <v>0.23</v>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
@@ -8223,7 +8223,7 @@
         <v>1</v>
       </c>
       <c r="AE74" t="n">
-        <v>0.848</v>
+        <v>0.904</v>
       </c>
       <c r="AF74" t="inlineStr">
         <is>
@@ -8322,7 +8322,7 @@
         <v>3</v>
       </c>
       <c r="Z75" t="n">
-        <v>1</v>
+        <v>0.948</v>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
@@ -8576,7 +8576,7 @@
         <v>5</v>
       </c>
       <c r="AJ77" t="n">
-        <v>0.806</v>
+        <v>0.86</v>
       </c>
       <c r="AK77" t="inlineStr">
         <is>
@@ -8887,7 +8887,7 @@
         <v>2</v>
       </c>
       <c r="Z80" t="n">
-        <v>0.515</v>
+        <v>0.412</v>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
@@ -8915,7 +8915,7 @@
         <v>2</v>
       </c>
       <c r="AJ80" t="n">
-        <v>0.515</v>
+        <v>0.412</v>
       </c>
       <c r="AK80" t="inlineStr">
         <is>
@@ -9141,7 +9141,7 @@
         <v>6</v>
       </c>
       <c r="AJ82" t="n">
-        <v>0.953</v>
+        <v>0.981</v>
       </c>
       <c r="AK82" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
         <v>8</v>
       </c>
       <c r="Z83" t="n">
-        <v>0.981</v>
+        <v>1</v>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
@@ -9480,7 +9480,7 @@
         <v>8</v>
       </c>
       <c r="AJ85" t="n">
-        <v>0.992</v>
+        <v>0.881</v>
       </c>
       <c r="AK85" t="inlineStr">
         <is>
@@ -9820,7 +9820,7 @@
         <v>5</v>
       </c>
       <c r="AJ89" t="n">
-        <v>0.343</v>
+        <v>0.275</v>
       </c>
       <c r="AK89" t="inlineStr">
         <is>
@@ -9905,7 +9905,7 @@
         <v>3</v>
       </c>
       <c r="Z90" t="n">
-        <v>0.156</v>
+        <v>0.178</v>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
@@ -9919,7 +9919,7 @@
         <v>2</v>
       </c>
       <c r="AE90" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.729</v>
       </c>
       <c r="AF90" t="inlineStr">
         <is>
@@ -10357,7 +10357,7 @@
         <v>2</v>
       </c>
       <c r="Z94" t="n">
-        <v>0.42</v>
+        <v>0.504</v>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
@@ -10381,15 +10381,15 @@
       <c r="AH94" t="n">
         <v>0.008840000000000001</v>
       </c>
-      <c r="AI94" s="3" t="n">
+      <c r="AI94" t="n">
         <v>3</v>
       </c>
-      <c r="AJ94" s="3" t="n">
-        <v>0.0442</v>
-      </c>
-      <c r="AK94" s="3" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="AJ94" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="AK94" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -10470,7 +10470,7 @@
         <v>5</v>
       </c>
       <c r="Z95" t="n">
-        <v>0.79</v>
+        <v>0.948</v>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
@@ -10498,7 +10498,7 @@
         <v>1</v>
       </c>
       <c r="AJ95" s="3" t="n">
-        <v>0.0152</v>
+        <v>0.0182</v>
       </c>
       <c r="AK95" s="3" t="inlineStr">
         <is>
@@ -10950,7 +10950,7 @@
         <v>10</v>
       </c>
       <c r="AJ99" t="n">
-        <v>0.953</v>
+        <v>0.981</v>
       </c>
       <c r="AK99" t="inlineStr">
         <is>
@@ -11035,7 +11035,7 @@
         <v>1</v>
       </c>
       <c r="Z100" t="n">
-        <v>0.537</v>
+        <v>0.43</v>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
@@ -11063,7 +11063,7 @@
         <v>2</v>
       </c>
       <c r="AJ100" t="n">
-        <v>0.0587</v>
+        <v>0.09379999999999999</v>
       </c>
       <c r="AK100" t="inlineStr">
         <is>
@@ -11261,7 +11261,7 @@
         <v>4</v>
       </c>
       <c r="Z102" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
@@ -11289,7 +11289,7 @@
         <v>4</v>
       </c>
       <c r="AJ102" t="n">
-        <v>0.327</v>
+        <v>0.262</v>
       </c>
       <c r="AK102" t="inlineStr">
         <is>
@@ -11402,7 +11402,7 @@
         <v>8</v>
       </c>
       <c r="AJ103" t="n">
-        <v>0.752</v>
+        <v>0.773</v>
       </c>
       <c r="AK103" t="inlineStr">
         <is>
@@ -11515,7 +11515,7 @@
         <v>9</v>
       </c>
       <c r="AJ104" t="n">
-        <v>0.737</v>
+        <v>0.736</v>
       </c>
       <c r="AK104" t="inlineStr">
         <is>
@@ -15627,7 +15627,7 @@
         <v>3</v>
       </c>
       <c r="I2" t="n">
-        <v>0.156</v>
+        <v>0.153</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -15641,7 +15641,7 @@
         <v>9</v>
       </c>
       <c r="N2" t="n">
-        <v>0.672</v>
+        <v>0.648</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0424</v>
+        <v>0.0339</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -15669,7 +15669,7 @@
         <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0806</v>
+        <v>0.067</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -15706,7 +15706,7 @@
         <v>4</v>
       </c>
       <c r="I3" t="n">
-        <v>0.233</v>
+        <v>0.229</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -15720,7 +15720,7 @@
         <v>8</v>
       </c>
       <c r="N3" t="n">
-        <v>0.645</v>
+        <v>0.626</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -15748,7 +15748,7 @@
         <v>3</v>
       </c>
       <c r="X3" t="n">
-        <v>0.156</v>
+        <v>0.153</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -15785,7 +15785,7 @@
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>0.143</v>
+        <v>0.137</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -15799,7 +15799,7 @@
         <v>5</v>
       </c>
       <c r="N4" t="n">
-        <v>0.49</v>
+        <v>0.491</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -15827,7 +15827,7 @@
         <v>2</v>
       </c>
       <c r="X4" t="n">
-        <v>0.156</v>
+        <v>0.153</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -15864,7 +15864,7 @@
         <v>2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.156</v>
+        <v>0.153</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -15878,7 +15878,7 @@
         <v>1</v>
       </c>
       <c r="N5" t="n">
-        <v>0.109</v>
+        <v>0.102</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -15892,7 +15892,7 @@
         <v>9</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9</v>
+        <v>0.896</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -15906,7 +15906,7 @@
         <v>8</v>
       </c>
       <c r="X5" t="n">
-        <v>0.423</v>
+        <v>0.42</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -15943,7 +15943,7 @@
         <v>8</v>
       </c>
       <c r="I6" t="n">
-        <v>0.497</v>
+        <v>0.491</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -15957,7 +15957,7 @@
         <v>4</v>
       </c>
       <c r="N6" t="n">
-        <v>0.358</v>
+        <v>0.354</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -15971,7 +15971,7 @@
         <v>4</v>
       </c>
       <c r="S6" t="n">
-        <v>0.109</v>
+        <v>0.102</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -15985,7 +15985,7 @@
         <v>4</v>
       </c>
       <c r="X6" t="n">
-        <v>0.156</v>
+        <v>0.153</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -16022,7 +16022,7 @@
         <v>9</v>
       </c>
       <c r="I7" t="n">
-        <v>0.66</v>
+        <v>0.639</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -16036,7 +16036,7 @@
         <v>2</v>
       </c>
       <c r="N7" t="n">
-        <v>0.143</v>
+        <v>0.137</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -16050,7 +16050,7 @@
         <v>5</v>
       </c>
       <c r="S7" t="n">
-        <v>0.233</v>
+        <v>0.225</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -16064,7 +16064,7 @@
         <v>6</v>
       </c>
       <c r="X7" t="n">
-        <v>0.371</v>
+        <v>0.364</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -16101,7 +16101,7 @@
         <v>5</v>
       </c>
       <c r="I8" t="n">
-        <v>0.268</v>
+        <v>0.261</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -16115,7 +16115,7 @@
         <v>3</v>
       </c>
       <c r="N8" t="n">
-        <v>0.156</v>
+        <v>0.153</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -16129,7 +16129,7 @@
         <v>8</v>
       </c>
       <c r="S8" t="n">
-        <v>0.704</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -16180,7 +16180,7 @@
         <v>7</v>
       </c>
       <c r="I9" t="n">
-        <v>0.328</v>
+        <v>0.326</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -16194,7 +16194,7 @@
         <v>6</v>
       </c>
       <c r="N9" t="n">
-        <v>0.497</v>
+        <v>0.491</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -16208,7 +16208,7 @@
         <v>6</v>
       </c>
       <c r="S9" t="n">
-        <v>0.583</v>
+        <v>0.571</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -16222,7 +16222,7 @@
         <v>5</v>
       </c>
       <c r="X9" t="n">
-        <v>0.178</v>
+        <v>0.172</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -16259,7 +16259,7 @@
         <v>6</v>
       </c>
       <c r="I10" t="n">
-        <v>0.319</v>
+        <v>0.303</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -16273,7 +16273,7 @@
         <v>7</v>
       </c>
       <c r="N10" t="n">
-        <v>0.505</v>
+        <v>0.497</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -16287,7 +16287,7 @@
         <v>7</v>
       </c>
       <c r="S10" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.677</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -16339,7 +16339,7 @@
         <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -16367,7 +16367,7 @@
         <v>1</v>
       </c>
       <c r="S12" t="n">
-        <v>0.009180000000000001</v>
+        <v>0.00734</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -16381,7 +16381,7 @@
         <v>1</v>
       </c>
       <c r="X12" t="n">
-        <v>0.0333</v>
+        <v>0.0314</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -16418,7 +16418,7 @@
         <v>4</v>
       </c>
       <c r="I13" t="n">
-        <v>0.177</v>
+        <v>0.166</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -16432,7 +16432,7 @@
         <v>6</v>
       </c>
       <c r="N13" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -16446,7 +16446,7 @@
         <v>2</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0333</v>
+        <v>0.0355</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -16460,7 +16460,7 @@
         <v>2</v>
       </c>
       <c r="X13" t="n">
-        <v>0.112</v>
+        <v>0.116</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -16497,7 +16497,7 @@
         <v>2</v>
       </c>
       <c r="I14" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -16539,7 +16539,7 @@
         <v>6</v>
       </c>
       <c r="X14" t="n">
-        <v>0.287</v>
+        <v>0.265</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -16576,7 +16576,7 @@
         <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>0.112</v>
+        <v>0.116</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -16590,7 +16590,7 @@
         <v>9</v>
       </c>
       <c r="N15" t="n">
-        <v>0.486</v>
+        <v>0.47</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -16604,7 +16604,7 @@
         <v>3</v>
       </c>
       <c r="S15" t="n">
-        <v>0.09</v>
+        <v>0.096</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -16655,7 +16655,7 @@
         <v>9</v>
       </c>
       <c r="I16" t="n">
-        <v>0.599</v>
+        <v>0.573</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -16669,7 +16669,7 @@
         <v>2</v>
       </c>
       <c r="N16" t="n">
-        <v>0.112</v>
+        <v>0.116</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -16683,7 +16683,7 @@
         <v>4</v>
       </c>
       <c r="S16" t="n">
-        <v>0.112</v>
+        <v>0.116</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -16697,7 +16697,7 @@
         <v>4</v>
       </c>
       <c r="X16" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -16734,7 +16734,7 @@
         <v>6</v>
       </c>
       <c r="I17" t="n">
-        <v>0.231</v>
+        <v>0.216</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -16748,7 +16748,7 @@
         <v>3</v>
       </c>
       <c r="N17" t="n">
-        <v>0.112</v>
+        <v>0.116</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -16762,7 +16762,7 @@
         <v>7</v>
       </c>
       <c r="S17" t="n">
-        <v>0.468</v>
+        <v>0.455</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -16776,7 +16776,7 @@
         <v>9</v>
       </c>
       <c r="X17" t="n">
-        <v>0.504</v>
+        <v>0.485</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -16813,7 +16813,7 @@
         <v>8</v>
       </c>
       <c r="I18" t="n">
-        <v>0.468</v>
+        <v>0.455</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -16827,7 +16827,7 @@
         <v>4</v>
       </c>
       <c r="N18" t="n">
-        <v>0.112</v>
+        <v>0.116</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -16841,7 +16841,7 @@
         <v>5</v>
       </c>
       <c r="S18" t="n">
-        <v>0.193</v>
+        <v>0.184</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -16855,7 +16855,7 @@
         <v>7</v>
       </c>
       <c r="X18" t="n">
-        <v>0.468</v>
+        <v>0.455</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -16892,7 +16892,7 @@
         <v>7</v>
       </c>
       <c r="I19" t="n">
-        <v>0.395</v>
+        <v>0.388</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -16906,7 +16906,7 @@
         <v>8</v>
       </c>
       <c r="N19" t="n">
-        <v>0.451</v>
+        <v>0.441</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -16920,7 +16920,7 @@
         <v>6</v>
       </c>
       <c r="S19" t="n">
-        <v>0.468</v>
+        <v>0.455</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -16934,7 +16934,7 @@
         <v>5</v>
       </c>
       <c r="X19" t="n">
-        <v>0.183</v>
+        <v>0.177</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -16971,7 +16971,7 @@
         <v>5</v>
       </c>
       <c r="I20" t="n">
-        <v>0.197</v>
+        <v>0.187</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -16985,7 +16985,7 @@
         <v>7</v>
       </c>
       <c r="N20" t="n">
-        <v>0.2</v>
+        <v>0.189</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -16999,7 +16999,7 @@
         <v>8</v>
       </c>
       <c r="S20" t="n">
-        <v>0.733</v>
+        <v>0.736</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -17013,7 +17013,7 @@
         <v>8</v>
       </c>
       <c r="X20" t="n">
-        <v>0.468</v>
+        <v>0.455</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
